--- a/pandemic-loss-modeling/data/epidemics_marani_240914_family.xlsx
+++ b/pandemic-loss-modeling/data/epidemics_marani_240914_family.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2375" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2454" uniqueCount="442">
   <si>
     <t>location</t>
   </si>
@@ -1307,6 +1307,9 @@
   </si>
   <si>
     <t>animalcontact/bite</t>
+  </si>
+  <si>
+    <t>poxviridae</t>
   </si>
   <si>
     <t>orthomyxoviridae</t>
@@ -1934,6 +1937,9 @@
       <c r="O5">
         <v>0</v>
       </c>
+      <c r="P5" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
@@ -1982,7 +1988,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2266,6 +2272,9 @@
       <c r="O12">
         <v>0</v>
       </c>
+      <c r="P12" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" t="s">
@@ -2360,6 +2369,9 @@
       <c r="O14">
         <v>1</v>
       </c>
+      <c r="P14" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" t="s">
@@ -2455,7 +2467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
         <v>31</v>
       </c>
@@ -2502,7 +2514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -2549,7 +2561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -2596,7 +2608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -2643,7 +2655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:16">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -2690,7 +2702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -2737,7 +2749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:16">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -2784,7 +2796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:16">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -2831,7 +2843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:16">
       <c r="A25" t="s">
         <v>37</v>
       </c>
@@ -2878,7 +2890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:15">
+    <row r="26" spans="1:16">
       <c r="A26" t="s">
         <v>38</v>
       </c>
@@ -2924,8 +2936,11 @@
       <c r="O26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:15">
+      <c r="P26" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -2972,7 +2987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" spans="1:16">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -3019,7 +3034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:16">
       <c r="A29" t="s">
         <v>41</v>
       </c>
@@ -3066,7 +3081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:16">
       <c r="A30" t="s">
         <v>42</v>
       </c>
@@ -3113,7 +3128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:16">
       <c r="A31" t="s">
         <v>43</v>
       </c>
@@ -3159,8 +3174,11 @@
       <c r="O31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:15">
+      <c r="P31" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
       <c r="A32" t="s">
         <v>24</v>
       </c>
@@ -4005,6 +4023,9 @@
       <c r="O49">
         <v>0</v>
       </c>
+      <c r="P49" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="50" spans="1:16">
       <c r="A50" t="s">
@@ -4053,7 +4074,7 @@
         <v>0</v>
       </c>
       <c r="P50" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4243,6 +4264,9 @@
       <c r="O54">
         <v>0</v>
       </c>
+      <c r="P54" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="55" spans="1:16">
       <c r="A55" t="s">
@@ -4337,6 +4361,9 @@
       <c r="O56">
         <v>0</v>
       </c>
+      <c r="P56" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="57" spans="1:16">
       <c r="A57" t="s">
@@ -4525,6 +4552,9 @@
       <c r="O60">
         <v>0</v>
       </c>
+      <c r="P60" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="61" spans="1:16">
       <c r="A61" t="s">
@@ -4620,7 +4650,7 @@
         <v>0</v>
       </c>
       <c r="P62" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4717,7 +4747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:15">
+    <row r="65" spans="1:16">
       <c r="A65" t="s">
         <v>70</v>
       </c>
@@ -4764,7 +4794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:15">
+    <row r="66" spans="1:16">
       <c r="A66" t="s">
         <v>71</v>
       </c>
@@ -4811,7 +4841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:15">
+    <row r="67" spans="1:16">
       <c r="A67" t="s">
         <v>21</v>
       </c>
@@ -4858,7 +4888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:15">
+    <row r="68" spans="1:16">
       <c r="A68" t="s">
         <v>21</v>
       </c>
@@ -4905,7 +4935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:15">
+    <row r="69" spans="1:16">
       <c r="A69" t="s">
         <v>72</v>
       </c>
@@ -4952,7 +4982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:15">
+    <row r="70" spans="1:16">
       <c r="A70" t="s">
         <v>73</v>
       </c>
@@ -4999,7 +5029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:15">
+    <row r="71" spans="1:16">
       <c r="A71" t="s">
         <v>74</v>
       </c>
@@ -5046,7 +5076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:15">
+    <row r="72" spans="1:16">
       <c r="A72" t="s">
         <v>75</v>
       </c>
@@ -5092,8 +5122,11 @@
       <c r="O72">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:15">
+      <c r="P72" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16">
       <c r="A73" t="s">
         <v>76</v>
       </c>
@@ -5140,7 +5173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:15">
+    <row r="74" spans="1:16">
       <c r="A74" t="s">
         <v>77</v>
       </c>
@@ -5187,7 +5220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:15">
+    <row r="75" spans="1:16">
       <c r="A75" t="s">
         <v>78</v>
       </c>
@@ -5234,7 +5267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:15">
+    <row r="76" spans="1:16">
       <c r="A76" t="s">
         <v>48</v>
       </c>
@@ -5281,7 +5314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:15">
+    <row r="77" spans="1:16">
       <c r="A77" t="s">
         <v>23</v>
       </c>
@@ -5328,7 +5361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:15">
+    <row r="78" spans="1:16">
       <c r="A78" t="s">
         <v>79</v>
       </c>
@@ -5375,7 +5408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:15">
+    <row r="79" spans="1:16">
       <c r="A79" t="s">
         <v>80</v>
       </c>
@@ -5421,8 +5454,11 @@
       <c r="O79">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:15">
+      <c r="P79" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16">
       <c r="A80" t="s">
         <v>81</v>
       </c>
@@ -5515,6 +5551,9 @@
       <c r="O81">
         <v>0</v>
       </c>
+      <c r="P81" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="82" spans="1:16">
       <c r="A82" t="s">
@@ -5610,7 +5649,7 @@
         <v>0</v>
       </c>
       <c r="P83" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5895,7 +5934,7 @@
         <v>0</v>
       </c>
       <c r="P89" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5944,6 +5983,9 @@
       <c r="O90">
         <v>0</v>
       </c>
+      <c r="P90" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="91" spans="1:16">
       <c r="A91" t="s">
@@ -6086,7 +6128,7 @@
         <v>0</v>
       </c>
       <c r="P93" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6182,6 +6224,9 @@
       <c r="O95">
         <v>1</v>
       </c>
+      <c r="P95" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="96" spans="1:16">
       <c r="A96" t="s">
@@ -6418,7 +6463,7 @@
         <v>0</v>
       </c>
       <c r="P100" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6561,6 +6606,9 @@
       <c r="O103">
         <v>0</v>
       </c>
+      <c r="P103" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="104" spans="1:16">
       <c r="A104" t="s">
@@ -6843,6 +6891,9 @@
       <c r="O109">
         <v>0</v>
       </c>
+      <c r="P109" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="110" spans="1:16">
       <c r="A110" t="s">
@@ -6938,7 +6989,7 @@
         <v>0</v>
       </c>
       <c r="P111" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7129,7 +7180,7 @@
         <v>0</v>
       </c>
       <c r="P115" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7273,7 +7324,7 @@
         <v>0</v>
       </c>
       <c r="P118" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7369,6 +7420,9 @@
       <c r="O120">
         <v>0</v>
       </c>
+      <c r="P120" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="121" spans="1:16">
       <c r="A121" t="s">
@@ -7417,7 +7471,7 @@
         <v>0</v>
       </c>
       <c r="P121" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7561,7 +7615,7 @@
         <v>0</v>
       </c>
       <c r="P124" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7657,6 +7711,9 @@
       <c r="O126">
         <v>0</v>
       </c>
+      <c r="P126" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="127" spans="1:16">
       <c r="A127" t="s">
@@ -7705,7 +7762,7 @@
         <v>0</v>
       </c>
       <c r="P127" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7755,7 +7812,7 @@
         <v>0</v>
       </c>
       <c r="P128" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7899,7 +7956,7 @@
         <v>0</v>
       </c>
       <c r="P131" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7949,7 +8006,7 @@
         <v>0</v>
       </c>
       <c r="P132" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7998,6 +8055,9 @@
       <c r="O133">
         <v>0</v>
       </c>
+      <c r="P133" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="134" spans="1:16">
       <c r="A134" t="s">
@@ -8092,6 +8152,9 @@
       <c r="O135">
         <v>0</v>
       </c>
+      <c r="P135" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="136" spans="1:16">
       <c r="A136" t="s">
@@ -8280,6 +8343,9 @@
       <c r="O139">
         <v>0</v>
       </c>
+      <c r="P139" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="140" spans="1:16">
       <c r="A140" t="s">
@@ -8516,7 +8582,7 @@
         <v>0</v>
       </c>
       <c r="P144" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8566,7 +8632,7 @@
         <v>0</v>
       </c>
       <c r="P145" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8616,7 +8682,7 @@
         <v>0</v>
       </c>
       <c r="P146" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8666,7 +8732,7 @@
         <v>0</v>
       </c>
       <c r="P147" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8716,7 +8782,7 @@
         <v>0</v>
       </c>
       <c r="P148" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8765,6 +8831,9 @@
       <c r="O149">
         <v>0</v>
       </c>
+      <c r="P149" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="150" spans="1:16">
       <c r="A150" t="s">
@@ -9048,7 +9117,7 @@
         <v>0</v>
       </c>
       <c r="P155" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9098,7 +9167,7 @@
         <v>0</v>
       </c>
       <c r="P156" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9242,7 +9311,7 @@
         <v>0</v>
       </c>
       <c r="P159" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9339,7 +9408,7 @@
         <v>0</v>
       </c>
       <c r="P161" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9436,7 +9505,7 @@
         <v>0</v>
       </c>
       <c r="P163" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9486,7 +9555,7 @@
         <v>0</v>
       </c>
       <c r="P164" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9676,6 +9745,9 @@
       <c r="O168">
         <v>0</v>
       </c>
+      <c r="P168" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="169" spans="1:16">
       <c r="A169" t="s">
@@ -9724,7 +9796,7 @@
         <v>0</v>
       </c>
       <c r="P169" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9773,6 +9845,9 @@
       <c r="O170">
         <v>0</v>
       </c>
+      <c r="P170" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="171" spans="1:16">
       <c r="A171" t="s">
@@ -9867,6 +9942,9 @@
       <c r="O172">
         <v>0</v>
       </c>
+      <c r="P172" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="173" spans="1:16">
       <c r="A173" t="s">
@@ -9962,7 +10040,7 @@
         <v>0</v>
       </c>
       <c r="P174" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10012,7 +10090,7 @@
         <v>0</v>
       </c>
       <c r="P175" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10062,7 +10140,7 @@
         <v>0</v>
       </c>
       <c r="P176" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10111,6 +10189,9 @@
       <c r="O177">
         <v>0</v>
       </c>
+      <c r="P177" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="178" spans="1:16">
       <c r="A178" t="s">
@@ -10205,6 +10286,9 @@
       <c r="O179">
         <v>1</v>
       </c>
+      <c r="P179" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="180" spans="1:16">
       <c r="A180" t="s">
@@ -10253,7 +10337,7 @@
         <v>0</v>
       </c>
       <c r="P180" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10350,7 +10434,7 @@
         <v>0</v>
       </c>
       <c r="P182" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10399,6 +10483,9 @@
       <c r="O183">
         <v>0</v>
       </c>
+      <c r="P183" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="184" spans="1:16">
       <c r="A184" t="s">
@@ -10540,6 +10627,9 @@
       <c r="O186">
         <v>0</v>
       </c>
+      <c r="P186" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="187" spans="1:16">
       <c r="A187" t="s">
@@ -10635,7 +10725,7 @@
         <v>0</v>
       </c>
       <c r="P188" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10684,6 +10774,9 @@
       <c r="O189">
         <v>1</v>
       </c>
+      <c r="P189" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="190" spans="1:16">
       <c r="A190" t="s">
@@ -10732,7 +10825,7 @@
         <v>0</v>
       </c>
       <c r="P190" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10782,7 +10875,7 @@
         <v>0</v>
       </c>
       <c r="P191" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10831,6 +10924,9 @@
       <c r="O192">
         <v>0</v>
       </c>
+      <c r="P192" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="193" spans="1:16">
       <c r="A193" t="s">
@@ -10926,7 +11022,7 @@
         <v>0</v>
       </c>
       <c r="P194" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10975,6 +11071,9 @@
       <c r="O195">
         <v>0</v>
       </c>
+      <c r="P195" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="196" spans="1:16">
       <c r="A196" t="s">
@@ -11023,7 +11122,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11260,6 +11359,9 @@
       <c r="O201">
         <v>0</v>
       </c>
+      <c r="P201" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="202" spans="1:16">
       <c r="A202" t="s">
@@ -11308,7 +11410,7 @@
         <v>0</v>
       </c>
       <c r="P202" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11358,7 +11460,7 @@
         <v>0</v>
       </c>
       <c r="P203" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11408,7 +11510,7 @@
         <v>0</v>
       </c>
       <c r="P204" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11646,7 +11748,7 @@
         <v>0</v>
       </c>
       <c r="P209" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11696,7 +11798,7 @@
         <v>0</v>
       </c>
       <c r="P210" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11793,7 +11895,7 @@
         <v>0</v>
       </c>
       <c r="P212" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11843,7 +11945,7 @@
         <v>0</v>
       </c>
       <c r="P213" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11939,6 +12041,9 @@
       <c r="O215">
         <v>0</v>
       </c>
+      <c r="P215" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="216" spans="1:16">
       <c r="A216" t="s">
@@ -12080,6 +12185,9 @@
       <c r="O218">
         <v>0</v>
       </c>
+      <c r="P218" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="219" spans="1:16">
       <c r="A219" t="s">
@@ -12175,7 +12283,7 @@
         <v>0</v>
       </c>
       <c r="P220" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12272,7 +12380,7 @@
         <v>0</v>
       </c>
       <c r="P222" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12321,6 +12429,9 @@
       <c r="O223">
         <v>0</v>
       </c>
+      <c r="P223" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="224" spans="1:16">
       <c r="A224" t="s">
@@ -12416,7 +12527,7 @@
         <v>0</v>
       </c>
       <c r="P225" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12466,7 +12577,7 @@
         <v>0</v>
       </c>
       <c r="P226" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12516,7 +12627,7 @@
         <v>0</v>
       </c>
       <c r="P227" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12566,7 +12677,7 @@
         <v>0</v>
       </c>
       <c r="P228" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12615,6 +12726,9 @@
       <c r="O229">
         <v>0</v>
       </c>
+      <c r="P229" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="230" spans="1:16">
       <c r="A230" t="s">
@@ -12663,7 +12777,7 @@
         <v>0</v>
       </c>
       <c r="P230" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12854,7 +12968,7 @@
         <v>0</v>
       </c>
       <c r="P234" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13232,6 +13346,9 @@
       <c r="O242">
         <v>0</v>
       </c>
+      <c r="P242" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="243" spans="1:16">
       <c r="A243" t="s">
@@ -13327,7 +13444,7 @@
         <v>0</v>
       </c>
       <c r="P244" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13377,7 +13494,7 @@
         <v>0</v>
       </c>
       <c r="P245" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13427,7 +13544,7 @@
         <v>0</v>
       </c>
       <c r="P246" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13523,6 +13640,9 @@
       <c r="O248">
         <v>0</v>
       </c>
+      <c r="P248" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="249" spans="1:16">
       <c r="A249" t="s">
@@ -13900,7 +14020,7 @@
         <v>0</v>
       </c>
       <c r="P256" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -13950,7 +14070,7 @@
         <v>0</v>
       </c>
       <c r="P257" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -13999,6 +14119,9 @@
       <c r="O258">
         <v>0</v>
       </c>
+      <c r="P258" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="259" spans="1:16">
       <c r="A259" t="s">
@@ -14093,6 +14216,9 @@
       <c r="O260">
         <v>0</v>
       </c>
+      <c r="P260" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="261" spans="1:16">
       <c r="A261" t="s">
@@ -14141,7 +14267,7 @@
         <v>0</v>
       </c>
       <c r="P261" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14285,7 +14411,7 @@
         <v>0</v>
       </c>
       <c r="P264" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14334,6 +14460,9 @@
       <c r="O265">
         <v>0</v>
       </c>
+      <c r="P265" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="266" spans="1:16">
       <c r="A266" t="s">
@@ -14382,7 +14511,7 @@
         <v>0</v>
       </c>
       <c r="P266" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14432,7 +14561,7 @@
         <v>0</v>
       </c>
       <c r="P267" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14482,7 +14611,7 @@
         <v>0</v>
       </c>
       <c r="P268" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14532,7 +14661,7 @@
         <v>0</v>
       </c>
       <c r="P269" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14629,7 +14758,7 @@
         <v>0</v>
       </c>
       <c r="P271" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -14678,6 +14807,9 @@
       <c r="O272">
         <v>0</v>
       </c>
+      <c r="P272" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="273" spans="1:16">
       <c r="A273" t="s">
@@ -14772,6 +14904,9 @@
       <c r="O274">
         <v>0</v>
       </c>
+      <c r="P274" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="275" spans="1:16">
       <c r="A275" t="s">
@@ -14866,6 +15001,9 @@
       <c r="O276">
         <v>0</v>
       </c>
+      <c r="P276" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="277" spans="1:16">
       <c r="A277" t="s">
@@ -14961,7 +15099,7 @@
         <v>0</v>
       </c>
       <c r="P278" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15105,7 +15243,7 @@
         <v>0</v>
       </c>
       <c r="P281" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15202,7 +15340,7 @@
         <v>0</v>
       </c>
       <c r="P283" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15252,7 +15390,7 @@
         <v>0</v>
       </c>
       <c r="P284" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15490,7 +15628,7 @@
         <v>0</v>
       </c>
       <c r="P289" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -15540,7 +15678,7 @@
         <v>0</v>
       </c>
       <c r="P290" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -15637,7 +15775,7 @@
         <v>0</v>
       </c>
       <c r="P292" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -15687,7 +15825,7 @@
         <v>0</v>
       </c>
       <c r="P293" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -15784,7 +15922,7 @@
         <v>0</v>
       </c>
       <c r="P295" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -15833,6 +15971,9 @@
       <c r="O296">
         <v>0</v>
       </c>
+      <c r="P296" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="297" spans="1:16">
       <c r="A297" t="s">
@@ -15881,7 +16022,7 @@
         <v>0</v>
       </c>
       <c r="P297" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16025,7 +16166,7 @@
         <v>0</v>
       </c>
       <c r="P300" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16075,7 +16216,7 @@
         <v>0</v>
       </c>
       <c r="P301" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16171,6 +16312,9 @@
       <c r="O303">
         <v>0</v>
       </c>
+      <c r="P303" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="304" spans="1:16">
       <c r="A304" t="s">
@@ -16218,6 +16362,9 @@
       <c r="O304">
         <v>0</v>
       </c>
+      <c r="P304" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="305" spans="1:16">
       <c r="A305" t="s">
@@ -16407,7 +16554,7 @@
         <v>0</v>
       </c>
       <c r="P308" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16503,6 +16650,9 @@
       <c r="O310">
         <v>0</v>
       </c>
+      <c r="P310" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="311" spans="1:16">
       <c r="A311" t="s">
@@ -16597,6 +16747,9 @@
       <c r="O312">
         <v>0</v>
       </c>
+      <c r="P312" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="313" spans="1:16">
       <c r="A313" t="s">
@@ -16645,7 +16798,7 @@
         <v>0</v>
       </c>
       <c r="P313" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -16788,6 +16941,9 @@
       <c r="O316">
         <v>0</v>
       </c>
+      <c r="P316" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="317" spans="1:16">
       <c r="A317" t="s">
@@ -16835,6 +16991,9 @@
       <c r="O317">
         <v>0</v>
       </c>
+      <c r="P317" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="318" spans="1:16">
       <c r="A318" t="s">
@@ -16976,6 +17135,9 @@
       <c r="O320">
         <v>0</v>
       </c>
+      <c r="P320" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="321" spans="1:16">
       <c r="A321" t="s">
@@ -17023,6 +17185,9 @@
       <c r="O321">
         <v>0</v>
       </c>
+      <c r="P321" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="322" spans="1:16">
       <c r="A322" t="s">
@@ -17070,6 +17235,9 @@
       <c r="O322">
         <v>0</v>
       </c>
+      <c r="P322" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="323" spans="1:16">
       <c r="A323" t="s">
@@ -17117,6 +17285,9 @@
       <c r="O323">
         <v>1</v>
       </c>
+      <c r="P323" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="324" spans="1:16">
       <c r="A324" t="s">
@@ -17165,7 +17336,7 @@
         <v>0</v>
       </c>
       <c r="P324" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17261,6 +17432,9 @@
       <c r="O326">
         <v>0</v>
       </c>
+      <c r="P326" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="327" spans="1:16">
       <c r="A327" t="s">
@@ -17450,7 +17624,7 @@
         <v>0</v>
       </c>
       <c r="P330" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -17688,7 +17862,7 @@
         <v>0</v>
       </c>
       <c r="P335" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -17737,6 +17911,9 @@
       <c r="O336">
         <v>0</v>
       </c>
+      <c r="P336" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="337" spans="1:16">
       <c r="A337" t="s">
@@ -17785,7 +17962,7 @@
         <v>0</v>
       </c>
       <c r="P337" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -17835,7 +18012,7 @@
         <v>0</v>
       </c>
       <c r="P338" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -17931,6 +18108,9 @@
       <c r="O340">
         <v>0</v>
       </c>
+      <c r="P340" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="341" spans="1:16">
       <c r="A341" t="s">
@@ -18072,6 +18252,9 @@
       <c r="O343">
         <v>0</v>
       </c>
+      <c r="P343" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="344" spans="1:16">
       <c r="A344" t="s">
@@ -18119,6 +18302,9 @@
       <c r="O344">
         <v>0</v>
       </c>
+      <c r="P344" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="345" spans="1:16">
       <c r="A345" t="s">
@@ -18166,6 +18352,9 @@
       <c r="O345">
         <v>0</v>
       </c>
+      <c r="P345" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="346" spans="1:16">
       <c r="A346" t="s">
@@ -18261,7 +18450,7 @@
         <v>0</v>
       </c>
       <c r="P347" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18310,6 +18499,9 @@
       <c r="O348">
         <v>0</v>
       </c>
+      <c r="P348" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="349" spans="1:16">
       <c r="A349" t="s">
@@ -18358,7 +18550,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -18408,7 +18600,7 @@
         <v>0</v>
       </c>
       <c r="P350" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -18458,7 +18650,7 @@
         <v>0</v>
       </c>
       <c r="P351" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -18507,6 +18699,9 @@
       <c r="O352">
         <v>0</v>
       </c>
+      <c r="P352" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="353" spans="1:16">
       <c r="A353" t="s">
@@ -18554,6 +18749,9 @@
       <c r="O353">
         <v>0</v>
       </c>
+      <c r="P353" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="354" spans="1:16">
       <c r="A354" t="s">
@@ -18602,7 +18800,7 @@
         <v>0</v>
       </c>
       <c r="P354" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -18652,7 +18850,7 @@
         <v>0</v>
       </c>
       <c r="P355" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -18889,6 +19087,9 @@
       <c r="O360">
         <v>0</v>
       </c>
+      <c r="P360" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="361" spans="1:16">
       <c r="A361" t="s">
@@ -18984,7 +19185,7 @@
         <v>0</v>
       </c>
       <c r="P362" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19175,7 +19376,7 @@
         <v>0</v>
       </c>
       <c r="P366" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19225,7 +19426,7 @@
         <v>0</v>
       </c>
       <c r="P367" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19321,6 +19522,9 @@
       <c r="O369">
         <v>1</v>
       </c>
+      <c r="P369" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="370" spans="1:16">
       <c r="A370" t="s">
@@ -19416,7 +19620,7 @@
         <v>0</v>
       </c>
       <c r="P371" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -19607,7 +19811,7 @@
         <v>0</v>
       </c>
       <c r="P375" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -19657,7 +19861,7 @@
         <v>0</v>
       </c>
       <c r="P376" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -19801,7 +20005,7 @@
         <v>0</v>
       </c>
       <c r="P379" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -19850,6 +20054,9 @@
       <c r="O380">
         <v>0</v>
       </c>
+      <c r="P380" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="381" spans="1:16">
       <c r="A381" t="s">
@@ -19992,7 +20199,7 @@
         <v>0</v>
       </c>
       <c r="P383" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20042,7 +20249,7 @@
         <v>0</v>
       </c>
       <c r="P384" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20186,7 +20393,7 @@
         <v>0</v>
       </c>
       <c r="P387" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20236,7 +20443,7 @@
         <v>0</v>
       </c>
       <c r="P388" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20286,7 +20493,7 @@
         <v>0</v>
       </c>
       <c r="P389" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -20383,7 +20590,7 @@
         <v>0</v>
       </c>
       <c r="P391" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -20480,7 +20687,7 @@
         <v>0</v>
       </c>
       <c r="P393" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -20530,7 +20737,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -20580,7 +20787,7 @@
         <v>0</v>
       </c>
       <c r="P395" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -20630,7 +20837,7 @@
         <v>0</v>
       </c>
       <c r="P396" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -20774,7 +20981,7 @@
         <v>0</v>
       </c>
       <c r="P399" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -20871,7 +21078,7 @@
         <v>0</v>
       </c>
       <c r="P401" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -20920,6 +21127,9 @@
       <c r="O402">
         <v>0</v>
       </c>
+      <c r="P402" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="403" spans="1:16">
       <c r="A403" t="s">
@@ -21015,7 +21225,7 @@
         <v>0</v>
       </c>
       <c r="P404" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21065,7 +21275,7 @@
         <v>0</v>
       </c>
       <c r="P405" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21115,7 +21325,7 @@
         <v>0</v>
       </c>
       <c r="P406" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21165,7 +21375,7 @@
         <v>0</v>
       </c>
       <c r="P407" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21309,7 +21519,7 @@
         <v>0</v>
       </c>
       <c r="P410" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -21359,7 +21569,7 @@
         <v>0</v>
       </c>
       <c r="P411" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -21409,7 +21619,7 @@
         <v>0</v>
       </c>
       <c r="P412" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -21459,7 +21669,7 @@
         <v>0</v>
       </c>
       <c r="P413" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -21509,7 +21719,7 @@
         <v>0</v>
       </c>
       <c r="P414" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -21606,7 +21816,7 @@
         <v>0</v>
       </c>
       <c r="P416" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -21750,7 +21960,7 @@
         <v>0</v>
       </c>
       <c r="P419" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -21799,6 +22009,9 @@
       <c r="O420">
         <v>0</v>
       </c>
+      <c r="P420" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="421" spans="1:16">
       <c r="A421" t="s">
@@ -21847,7 +22060,7 @@
         <v>0</v>
       </c>
       <c r="P421" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -21944,7 +22157,7 @@
         <v>0</v>
       </c>
       <c r="P423" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -21994,7 +22207,7 @@
         <v>0</v>
       </c>
       <c r="P424" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22138,7 +22351,7 @@
         <v>0</v>
       </c>
       <c r="P427" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -22282,7 +22495,7 @@
         <v>0</v>
       </c>
       <c r="P430" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -22332,7 +22545,7 @@
         <v>0</v>
       </c>
       <c r="P431" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -22381,6 +22594,9 @@
       <c r="O432">
         <v>0</v>
       </c>
+      <c r="P432" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="433" spans="1:16">
       <c r="A433" t="s">
@@ -22476,7 +22692,7 @@
         <v>0</v>
       </c>
       <c r="P434" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -22526,7 +22742,7 @@
         <v>0</v>
       </c>
       <c r="P435" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -22576,7 +22792,7 @@
         <v>0</v>
       </c>
       <c r="P436" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -22673,7 +22889,7 @@
         <v>0</v>
       </c>
       <c r="P438" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -22723,7 +22939,7 @@
         <v>0</v>
       </c>
       <c r="P439" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -22820,7 +23036,7 @@
         <v>0</v>
       </c>
       <c r="P441" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -22870,7 +23086,7 @@
         <v>0</v>
       </c>
       <c r="P442" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -22920,7 +23136,7 @@
         <v>0</v>
       </c>
       <c r="P443" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23017,7 +23233,7 @@
         <v>0</v>
       </c>
       <c r="P445" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23114,7 +23330,7 @@
         <v>0</v>
       </c>
       <c r="P447" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23164,7 +23380,7 @@
         <v>0</v>
       </c>
       <c r="P448" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23214,7 +23430,7 @@
         <v>0</v>
       </c>
       <c r="P449" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -23264,7 +23480,7 @@
         <v>0</v>
       </c>
       <c r="P450" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -23408,7 +23624,7 @@
         <v>0</v>
       </c>
       <c r="P453" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -23646,7 +23862,7 @@
         <v>0</v>
       </c>
       <c r="P458" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -23790,7 +24006,7 @@
         <v>0</v>
       </c>
       <c r="P461" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -23886,6 +24102,9 @@
       <c r="O463">
         <v>0</v>
       </c>
+      <c r="P463" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="464" spans="1:16">
       <c r="A464" t="s">
@@ -24028,7 +24247,7 @@
         <v>0</v>
       </c>
       <c r="P466" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24077,6 +24296,9 @@
       <c r="O467">
         <v>0</v>
       </c>
+      <c r="P467" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="468" spans="1:16">
       <c r="A468" t="s">
@@ -24125,7 +24347,7 @@
         <v>0</v>
       </c>
       <c r="P468" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -24222,7 +24444,7 @@
         <v>0</v>
       </c>
       <c r="P470" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -24272,7 +24494,7 @@
         <v>0</v>
       </c>
       <c r="P471" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -24322,7 +24544,7 @@
         <v>0</v>
       </c>
       <c r="P472" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -24372,7 +24594,7 @@
         <v>0</v>
       </c>
       <c r="P473" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -24422,7 +24644,7 @@
         <v>0</v>
       </c>
       <c r="P474" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -24566,7 +24788,7 @@
         <v>0</v>
       </c>
       <c r="P477" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -24616,7 +24838,7 @@
         <v>0</v>
       </c>
       <c r="P478" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -24713,7 +24935,7 @@
         <v>0</v>
       </c>
       <c r="P480" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -24763,7 +24985,7 @@
         <v>0</v>
       </c>
       <c r="P481" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -24860,7 +25082,7 @@
         <v>0</v>
       </c>
       <c r="P483" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -24910,7 +25132,7 @@
         <v>0</v>
       </c>
       <c r="P484" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -24960,7 +25182,7 @@
         <v>0</v>
       </c>
       <c r="P485" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25056,6 +25278,9 @@
       <c r="O487">
         <v>0</v>
       </c>
+      <c r="P487" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="488" spans="1:16">
       <c r="A488" t="s">
@@ -25104,7 +25329,7 @@
         <v>0</v>
       </c>
       <c r="P488" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25154,7 +25379,7 @@
         <v>0</v>
       </c>
       <c r="P489" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -25204,7 +25429,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -25254,7 +25479,7 @@
         <v>0</v>
       </c>
       <c r="P491" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -25304,7 +25529,7 @@
         <v>0</v>
       </c>
       <c r="P492" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -25354,7 +25579,7 @@
         <v>0</v>
       </c>
       <c r="P493" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -25404,7 +25629,7 @@
         <v>0</v>
       </c>
       <c r="P494" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -25454,7 +25679,7 @@
         <v>0</v>
       </c>
       <c r="P495" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -25504,7 +25729,7 @@
         <v>0</v>
       </c>
       <c r="P496" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -25554,7 +25779,7 @@
         <v>0</v>
       </c>
       <c r="P497" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -25604,7 +25829,7 @@
         <v>0</v>
       </c>
       <c r="P498" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -25701,7 +25926,7 @@
         <v>0</v>
       </c>
       <c r="P500" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -25751,7 +25976,7 @@
         <v>0</v>
       </c>
       <c r="P501" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -25801,7 +26026,7 @@
         <v>0</v>
       </c>
       <c r="P502" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -25898,7 +26123,7 @@
         <v>0</v>
       </c>
       <c r="P504" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -25947,6 +26172,9 @@
       <c r="O505">
         <v>0</v>
       </c>
+      <c r="P505" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="506" spans="1:16">
       <c r="A506" t="s">
@@ -25994,6 +26222,9 @@
       <c r="O506">
         <v>0</v>
       </c>
+      <c r="P506" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="507" spans="1:16">
       <c r="A507" t="s">
@@ -26042,7 +26273,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26092,7 +26323,7 @@
         <v>0</v>
       </c>
       <c r="P508" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -26142,7 +26373,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -26192,7 +26423,7 @@
         <v>0</v>
       </c>
       <c r="P510" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -26288,6 +26519,9 @@
       <c r="O512">
         <v>0</v>
       </c>
+      <c r="P512" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="513" spans="1:16">
       <c r="A513" t="s">
@@ -26336,7 +26570,7 @@
         <v>0</v>
       </c>
       <c r="P513" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -26386,7 +26620,7 @@
         <v>0</v>
       </c>
       <c r="P514" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -26435,6 +26669,9 @@
       <c r="O515">
         <v>0</v>
       </c>
+      <c r="P515" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="516" spans="1:16">
       <c r="A516" t="s">
@@ -26483,7 +26720,7 @@
         <v>0</v>
       </c>
       <c r="P516" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -26533,7 +26770,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -26582,6 +26819,9 @@
       <c r="O518">
         <v>0</v>
       </c>
+      <c r="P518" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="519" spans="1:16">
       <c r="A519" t="s">
@@ -26677,7 +26917,7 @@
         <v>0</v>
       </c>
       <c r="P520" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -26774,7 +27014,7 @@
         <v>0</v>
       </c>
       <c r="P522" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -26824,7 +27064,7 @@
         <v>0</v>
       </c>
       <c r="P523" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -26874,7 +27114,7 @@
         <v>0</v>
       </c>
       <c r="P524" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -26971,7 +27211,7 @@
         <v>0</v>
       </c>
       <c r="P526" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27068,7 +27308,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -27212,7 +27452,7 @@
         <v>0</v>
       </c>
       <c r="P531" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -27262,7 +27502,7 @@
         <v>0</v>
       </c>
       <c r="P532" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -27406,7 +27646,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -27456,7 +27696,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -27506,7 +27746,7 @@
         <v>0</v>
       </c>
       <c r="P537" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -27556,7 +27796,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -27606,7 +27846,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -27656,7 +27896,7 @@
         <v>0</v>
       </c>
       <c r="P540" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -27706,7 +27946,7 @@
         <v>0</v>
       </c>
       <c r="P541" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -27756,7 +27996,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
